--- a/public/data/12-10-25/saintek.xlsx
+++ b/public/data/12-10-25/saintek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARVIN3108\Desktop\au-tryout-statistics\public\data\12-10-25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234320DA-10E4-495E-9120-44C8D13E5784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187B0F0C-247E-4B9E-91B4-5DED31B7A6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{61386F17-0FE2-4C08-8F1F-E087FCE032DB}"/>
   </bookViews>
@@ -68033,60 +68033,60 @@
         <v>5</v>
       </c>
       <c r="E833" s="5">
-        <f t="shared" ref="E833:E896" si="130">10/15*D833</f>
+        <f t="shared" ref="E833:E857" si="130">10/15*D833</f>
         <v>3.333333333333333</v>
       </c>
       <c r="F833" s="4">
         <v>3</v>
       </c>
       <c r="G833" s="5">
-        <f t="shared" ref="G833:G896" si="131">10/15*F833</f>
+        <f t="shared" ref="G833:G857" si="131">10/15*F833</f>
         <v>2</v>
       </c>
       <c r="H833" s="4">
         <v>4</v>
       </c>
       <c r="I833" s="5">
-        <f t="shared" ref="I833:I896" si="132">10/15*H833</f>
+        <f t="shared" ref="I833:I857" si="132">10/15*H833</f>
         <v>2.6666666666666665</v>
       </c>
       <c r="J833" s="4">
         <v>3</v>
       </c>
       <c r="K833" s="5">
-        <f t="shared" ref="K833:K896" si="133">10/15*J833</f>
+        <f t="shared" ref="K833:K857" si="133">10/15*J833</f>
         <v>2</v>
       </c>
       <c r="L833" s="4">
         <v>3</v>
       </c>
       <c r="M833" s="5">
-        <f t="shared" ref="M833:M896" si="134">10/15*L833</f>
+        <f t="shared" ref="M833:M857" si="134">10/15*L833</f>
         <v>2</v>
       </c>
       <c r="N833" s="4">
         <v>4</v>
       </c>
       <c r="O833" s="5">
-        <f t="shared" ref="O833:O896" si="135">10/15*N833</f>
+        <f t="shared" ref="O833:O857" si="135">10/15*N833</f>
         <v>2.6666666666666665</v>
       </c>
       <c r="P833" s="4">
         <v>3</v>
       </c>
       <c r="Q833" s="5">
-        <f t="shared" ref="Q833:Q896" si="136">10/15*P833</f>
+        <f t="shared" ref="Q833:Q857" si="136">10/15*P833</f>
         <v>2</v>
       </c>
       <c r="R833" s="4">
         <v>8</v>
       </c>
       <c r="S833" s="5">
-        <f t="shared" ref="S833:S896" si="137">10/15*R833</f>
+        <f t="shared" ref="S833:S857" si="137">10/15*R833</f>
         <v>5.333333333333333</v>
       </c>
       <c r="T833" s="2">
-        <f t="shared" ref="T833:T896" si="138">SUM(E833,G833,I833,K833,M833,O833,Q833,S833)</f>
+        <f t="shared" ref="T833:T857" si="138">SUM(E833,G833,I833,K833,M833,O833,Q833,S833)</f>
         <v>21.999999999999996</v>
       </c>
       <c r="U833" s="2">
